--- a/KIT-REPRISE/00-referentiels.xlsx
+++ b/KIT-REPRISE/00-referentiels.xlsx
@@ -436,21 +436,21 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>Services — Ville</v>
+        <v>Familles de risque (Document Unique)</v>
       </c>
       <c r="B2" t="str">
-        <v>Police municipale</v>
+        <v>Conduite d'engins de déneigement</v>
       </c>
       <c r="C2" t="str">
-        <v/>
+        <v>Déneigement de la voirie par engins, de nuit et par grand froid.</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="str">
-        <v>Services — Agglomération</v>
+        <v>Services — Ville</v>
       </c>
       <c r="B3" t="str">
-        <v>Transports urbains</v>
+        <v>Police municipale</v>
       </c>
       <c r="C3" t="str">
         <v/>
@@ -458,13 +458,13 @@
     </row>
     <row r="4">
       <c r="A4" t="str">
-        <v>Familles de risque (Document Unique)</v>
+        <v>Services — Agglomération</v>
       </c>
       <c r="B4" t="str">
-        <v>Conduite d'engins de déneigement</v>
+        <v>Transports urbains</v>
       </c>
       <c r="C4" t="str">
-        <v>Déneigement de la voirie par engins, de nuit et par grand froid.</v>
+        <v/>
       </c>
     </row>
   </sheetData>
@@ -513,7 +513,7 @@
         <v>Texte</v>
       </c>
       <c r="D2" t="str">
-        <v>Risques (Registre AT/MP) · Sièges de lésion · Natures de lésion · Statuts RH · Services — Ville · Services — Agglomération · Familles de risque (Document Unique) · Types d'accueil au poste</v>
+        <v>Risques (Registre AT/MP) · Sièges de lésion · Natures de lésion · Statuts RH · Familles de risque (Document Unique) · Types d'accueil au poste · Services — Ville · Services — Agglomération</v>
       </c>
       <c r="E2" t="str">
         <v>liste fermée : une valeur inconnue fait refuser la ligne</v>
